--- a/auxiliar_linha_producao_YPE/lista.m1alp.xlsx
+++ b/auxiliar_linha_producao_YPE/lista.m1alp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\auxiliar_linha_producao_YPE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F92C6CD4-DAED-4503-8165-41763902D94D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E7096F2-0628-4E2E-AAED-33AB9988D2D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6EE218CC-924D-4502-9B63-704B834FDA1C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="18">
   <si>
     <t>BEATRIZ SANTOS DO PRADO</t>
   </si>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>OK</t>
+  </si>
+  <si>
+    <t>Ok</t>
   </si>
 </sst>
 </file>
@@ -513,7 +516,9 @@
       <c r="D1" s="2">
         <v>46275</v>
       </c>
-      <c r="E1" s="1"/>
+      <c r="E1" s="2">
+        <v>46282</v>
+      </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -573,7 +578,9 @@
       <c r="C4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
@@ -589,8 +596,12 @@
       <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
+      <c r="C5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
@@ -609,7 +620,9 @@
       <c r="C6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="4"/>
+      <c r="D6" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
@@ -628,7 +641,9 @@
       <c r="C7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
@@ -647,7 +662,9 @@
       <c r="C8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
@@ -663,7 +680,9 @@
       <c r="B9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="4"/>
+      <c r="C9" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
@@ -683,7 +702,9 @@
       <c r="C10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
@@ -723,7 +744,9 @@
       <c r="C12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
@@ -739,8 +762,12 @@
       <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
+      <c r="C13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>17</v>
+      </c>
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
@@ -756,8 +783,12 @@
       <c r="B14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
+      <c r="C14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
@@ -776,7 +807,9 @@
       <c r="C15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="4"/>
+      <c r="D15" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
@@ -792,8 +825,12 @@
       <c r="B16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
+      <c r="C16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -821,23 +858,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="5961bfb0-077a-48f3-b3a8-28880a00c350" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010093213D9F94826D42BC9EF0DBA8180378" ma:contentTypeVersion="10" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="af650f022ad4c56918cd59f318082a35">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="5961bfb0-077a-48f3-b3a8-28880a00c350" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c862f0df734372448ddd1e114a488d17" ns3:_="">
     <xsd:import namespace="5961bfb0-077a-48f3-b3a8-28880a00c350"/>
@@ -1017,31 +1037,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CFD6CEB-A3F9-455C-8019-7855A3BB1AC4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="5961bfb0-077a-48f3-b3a8-28880a00c350"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E59E28A-43A4-4B94-AFD1-581E7FE347D0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="5961bfb0-077a-48f3-b3a8-28880a00c350" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BC20A4E-AA8D-41EC-8886-FD0F362DA293}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1057,4 +1070,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E59E28A-43A4-4B94-AFD1-581E7FE347D0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CFD6CEB-A3F9-455C-8019-7855A3BB1AC4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5961bfb0-077a-48f3-b3a8-28880a00c350"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/auxiliar_linha_producao_YPE/lista.m1alp.xlsx
+++ b/auxiliar_linha_producao_YPE/lista.m1alp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\auxiliar_linha_producao_YPE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E7096F2-0628-4E2E-AAED-33AB9988D2D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE83A07A-F19F-4385-81D8-E73844553DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6EE218CC-924D-4502-9B63-704B834FDA1C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="18">
   <si>
     <t>BEATRIZ SANTOS DO PRADO</t>
   </si>
@@ -539,7 +539,9 @@
       <c r="D2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="4"/>
+      <c r="E2" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
@@ -560,7 +562,9 @@
       <c r="D3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="4"/>
+      <c r="E3" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
@@ -683,7 +687,9 @@
       <c r="C9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
@@ -726,7 +732,9 @@
       <c r="D11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="4"/>
+      <c r="E11" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
@@ -858,6 +866,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="5961bfb0-077a-48f3-b3a8-28880a00c350" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010093213D9F94826D42BC9EF0DBA8180378" ma:contentTypeVersion="10" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="af650f022ad4c56918cd59f318082a35">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="5961bfb0-077a-48f3-b3a8-28880a00c350" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c862f0df734372448ddd1e114a488d17" ns3:_="">
     <xsd:import namespace="5961bfb0-077a-48f3-b3a8-28880a00c350"/>
@@ -1037,24 +1062,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CFD6CEB-A3F9-455C-8019-7855A3BB1AC4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5961bfb0-077a-48f3-b3a8-28880a00c350"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="5961bfb0-077a-48f3-b3a8-28880a00c350" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E59E28A-43A4-4B94-AFD1-581E7FE347D0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BC20A4E-AA8D-41EC-8886-FD0F362DA293}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1070,28 +1102,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E59E28A-43A4-4B94-AFD1-581E7FE347D0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CFD6CEB-A3F9-455C-8019-7855A3BB1AC4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="5961bfb0-077a-48f3-b3a8-28880a00c350"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/auxiliar_linha_producao_YPE/lista.m1alp.xlsx
+++ b/auxiliar_linha_producao_YPE/lista.m1alp.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\auxiliar_linha_producao_YPE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE83A07A-F19F-4385-81D8-E73844553DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{421F9317-CB4C-4318-BF82-08EA9A681110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6EE218CC-924D-4502-9B63-704B834FDA1C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="18">
   <si>
     <t>BEATRIZ SANTOS DO PRADO</t>
   </si>
@@ -606,7 +606,9 @@
       <c r="D5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="4"/>
+      <c r="E5" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
@@ -669,7 +671,9 @@
       <c r="D8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="4"/>
+      <c r="E8" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
@@ -797,7 +801,9 @@
       <c r="D14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="4"/>
+      <c r="E14" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
@@ -866,20 +872,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="5961bfb0-077a-48f3-b3a8-28880a00c350" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="5961bfb0-077a-48f3-b3a8-28880a00c350" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1063,6 +1069,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E59E28A-43A4-4B94-AFD1-581E7FE347D0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CFD6CEB-A3F9-455C-8019-7855A3BB1AC4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -1074,14 +1088,6 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="5961bfb0-077a-48f3-b3a8-28880a00c350"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E59E28A-43A4-4B94-AFD1-581E7FE347D0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/auxiliar_linha_producao_YPE/lista.m1alp.xlsx
+++ b/auxiliar_linha_producao_YPE/lista.m1alp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\auxiliar_linha_producao_YPE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{421F9317-CB4C-4318-BF82-08EA9A681110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C652E5-6FB5-4B83-96DD-FF032D38C9B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6EE218CC-924D-4502-9B63-704B834FDA1C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="18">
   <si>
     <t>BEATRIZ SANTOS DO PRADO</t>
   </si>
@@ -845,7 +845,9 @@
       <c r="D16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E16" s="4"/>
+      <c r="E16" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
@@ -872,23 +874,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="5961bfb0-077a-48f3-b3a8-28880a00c350" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010093213D9F94826D42BC9EF0DBA8180378" ma:contentTypeVersion="10" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="af650f022ad4c56918cd59f318082a35">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="5961bfb0-077a-48f3-b3a8-28880a00c350" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c862f0df734372448ddd1e114a488d17" ns3:_="">
     <xsd:import namespace="5961bfb0-077a-48f3-b3a8-28880a00c350"/>
@@ -1068,10 +1053,37 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="5961bfb0-077a-48f3-b3a8-28880a00c350" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E59E28A-43A4-4B94-AFD1-581E7FE347D0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BC20A4E-AA8D-41EC-8886-FD0F362DA293}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="5961bfb0-077a-48f3-b3a8-28880a00c350"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1093,19 +1105,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BC20A4E-AA8D-41EC-8886-FD0F362DA293}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E59E28A-43A4-4B94-AFD1-581E7FE347D0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="5961bfb0-077a-48f3-b3a8-28880a00c350"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/auxiliar_linha_producao_YPE/lista.m1alp.xlsx
+++ b/auxiliar_linha_producao_YPE/lista.m1alp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\auxiliar_linha_producao_YPE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C652E5-6FB5-4B83-96DD-FF032D38C9B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF278641-62BE-4B05-9957-8F8FD4D145DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6EE218CC-924D-4502-9B63-704B834FDA1C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="18">
   <si>
     <t>BEATRIZ SANTOS DO PRADO</t>
   </si>
@@ -824,7 +824,9 @@
       <c r="D15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E15" s="4"/>
+      <c r="E15" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
@@ -874,6 +876,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="5961bfb0-077a-48f3-b3a8-28880a00c350" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010093213D9F94826D42BC9EF0DBA8180378" ma:contentTypeVersion="10" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="af650f022ad4c56918cd59f318082a35">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="5961bfb0-077a-48f3-b3a8-28880a00c350" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c862f0df734372448ddd1e114a488d17" ns3:_="">
     <xsd:import namespace="5961bfb0-077a-48f3-b3a8-28880a00c350"/>
@@ -1053,14 +1063,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="5961bfb0-077a-48f3-b3a8-28880a00c350" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1071,6 +1073,22 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CFD6CEB-A3F9-455C-8019-7855A3BB1AC4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5961bfb0-077a-48f3-b3a8-28880a00c350"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8BC20A4E-AA8D-41EC-8886-FD0F362DA293}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1088,22 +1106,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CFD6CEB-A3F9-455C-8019-7855A3BB1AC4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="5961bfb0-077a-48f3-b3a8-28880a00c350"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E59E28A-43A4-4B94-AFD1-581E7FE347D0}">
   <ds:schemaRefs>

--- a/auxiliar_linha_producao_YPE/lista.m1alp.xlsx
+++ b/auxiliar_linha_producao_YPE/lista.m1alp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof. Luis\Documents\GitHub\senai2026\auxiliar_linha_producao_YPE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF278641-62BE-4B05-9957-8F8FD4D145DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F54F6FA-E17C-4CCF-9153-EBAF7D8E2312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{6EE218CC-924D-4502-9B63-704B834FDA1C}"/>
   </bookViews>
@@ -155,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -163,6 +163,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -497,7 +500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7E4E142-EB18-47C9-8CD6-5BE4D1390D4A}">
-  <dimension ref="A1:K17"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -542,7 +545,9 @@
       <c r="E2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="4"/>
+      <c r="F2" s="4">
+        <v>100</v>
+      </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
@@ -565,7 +570,9 @@
       <c r="E3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="4"/>
+      <c r="F3" s="4">
+        <v>65</v>
+      </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
@@ -586,7 +593,9 @@
         <v>16</v>
       </c>
       <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+      <c r="F4" s="4">
+        <v>65</v>
+      </c>
       <c r="G4" s="4"/>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
@@ -609,7 +618,9 @@
       <c r="E5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="4"/>
+      <c r="F5" s="4">
+        <v>75</v>
+      </c>
       <c r="G5" s="4"/>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
@@ -630,7 +641,9 @@
         <v>16</v>
       </c>
       <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+      <c r="F6" s="4">
+        <v>85</v>
+      </c>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
@@ -651,7 +664,9 @@
         <v>16</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
@@ -674,7 +689,9 @@
       <c r="E8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="4"/>
+      <c r="F8" s="4">
+        <v>60</v>
+      </c>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
@@ -695,7 +712,9 @@
         <v>16</v>
       </c>
       <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+      <c r="F9" s="4">
+        <v>75</v>
+      </c>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
@@ -716,7 +735,9 @@
         <v>16</v>
       </c>
       <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+      <c r="F10" s="4">
+        <v>85</v>
+      </c>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
@@ -739,7 +760,9 @@
       <c r="E11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F11" s="4"/>
+      <c r="F11" s="4">
+        <v>85</v>
+      </c>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
@@ -760,7 +783,9 @@
         <v>16</v>
       </c>
       <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
+      <c r="F12" s="4">
+        <v>95</v>
+      </c>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
@@ -781,7 +806,9 @@
         <v>17</v>
       </c>
       <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
+      <c r="F13" s="4">
+        <v>0</v>
+      </c>
       <c r="G13" s="4"/>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
@@ -804,7 +831,9 @@
       <c r="E14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="4"/>
+      <c r="F14" s="4">
+        <v>95</v>
+      </c>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
@@ -827,7 +856,9 @@
       <c r="E15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="4"/>
+      <c r="F15" s="4">
+        <v>75</v>
+      </c>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
@@ -850,7 +881,9 @@
       <c r="E16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F16" s="4"/>
+      <c r="F16" s="4">
+        <v>85</v>
+      </c>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
@@ -870,17 +903,24 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
     </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B18" s="5"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B19" s="5"/>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="5961bfb0-077a-48f3-b3a8-28880a00c350" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1064,26 +1104,17 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="5961bfb0-077a-48f3-b3a8-28880a00c350" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CFD6CEB-A3F9-455C-8019-7855A3BB1AC4}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E59E28A-43A4-4B94-AFD1-581E7FE347D0}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="5961bfb0-077a-48f3-b3a8-28880a00c350"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1107,9 +1138,17 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E59E28A-43A4-4B94-AFD1-581E7FE347D0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0CFD6CEB-A3F9-455C-8019-7855A3BB1AC4}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5961bfb0-077a-48f3-b3a8-28880a00c350"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>